--- a/Etapa Construcción - Iteración 1/Estimación 04 Caso Optimista - Kairos - NexTech.xlsx
+++ b/Etapa Construcción - Iteración 1/Estimación 04 Caso Optimista - Kairos - NexTech.xlsx
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="129">
   <si>
     <t>ESTIMACIÓN por PUNTOS de CASO de USO</t>
   </si>
@@ -321,55 +321,43 @@
     <t>Usuario con acceso a vistas</t>
   </si>
   <si>
-    <t>Toggl Track</t>
+    <t>Miembro</t>
+  </si>
+  <si>
+    <t>Sistema de inicio de sesión que interactua con el sistema</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peso Total Actores, sin ajustar (UAW) </t>
+  </si>
+  <si>
+    <t>2. PESO DE LOS CU</t>
+  </si>
+  <si>
+    <t>Casos de Uso</t>
+  </si>
+  <si>
+    <t>Comentario</t>
+  </si>
+  <si>
+    <t>Número de transacciones</t>
+  </si>
+  <si>
+    <t>Complejidad</t>
+  </si>
+  <si>
+    <t>CU07: Crear etapa</t>
   </si>
   <si>
     <t>Simple</t>
   </si>
   <si>
-    <t>Otro sistema con una API</t>
-  </si>
-  <si>
-    <t>Miembro</t>
-  </si>
-  <si>
-    <t>Sistema de inicio de sesión que interactua con el sistema</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peso Total Actores, sin ajustar (UAW) </t>
-  </si>
-  <si>
-    <t>2. PESO DE LOS CU</t>
-  </si>
-  <si>
-    <t>Casos de Uso</t>
-  </si>
-  <si>
-    <t>Comentario</t>
-  </si>
-  <si>
-    <t>Número de transacciones</t>
-  </si>
-  <si>
-    <t>Complejidad</t>
-  </si>
-  <si>
     <t>CU23: Registrar usuario a proyecto</t>
   </si>
   <si>
-    <t>CU05: Crear Proyecto</t>
-  </si>
-  <si>
     <t>CU##: Gestionar proyectos</t>
   </si>
   <si>
-    <t>CU08: Crear iteracion</t>
-  </si>
-  <si>
-    <t>CU07: Crear etapa</t>
-  </si>
-  <si>
-    <t>CU##: Gestionar iteraciones</t>
+    <t>CU08: Crear iteración</t>
   </si>
   <si>
     <t>CU##: Gestionar tareas</t>
@@ -752,7 +740,7 @@
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0\ %"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -793,6 +781,10 @@
       <sz val="12.0"/>
       <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
     </font>
     <font>
       <u/>
@@ -981,7 +973,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="88">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1083,11 +1075,34 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="9" fillId="3" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="9" fillId="3" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="9" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="9" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf borderId="9" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="9" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="9" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="9" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="12" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="12" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="12" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
@@ -1124,10 +1139,10 @@
     <xf borderId="9" fillId="3" fontId="5" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="4" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="9" fillId="4" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1160,7 +1175,7 @@
     <xf borderId="9" fillId="2" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="5" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="10" fillId="5" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="9" fillId="2" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -1196,7 +1211,7 @@
     <xf borderId="9" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="3" fontId="11" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="9" fillId="3" fontId="12" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="9" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1900,24 +1915,12 @@
     </row>
     <row r="10" ht="27.75" customHeight="1">
       <c r="A10" s="1"/>
-      <c r="B10" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="24">
-        <v>1.0</v>
-      </c>
-      <c r="F10" s="25">
-        <v>1.0</v>
-      </c>
-      <c r="G10" s="24">
-        <v>1.0</v>
-      </c>
+      <c r="B10" s="21"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="24"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
@@ -1941,13 +1944,13 @@
     <row r="11" ht="27.75" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="21" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C11" s="22" t="s">
         <v>13</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E11" s="24">
         <f>IF(C11="Simple",1,IF(C11="Intermedio",2,IF(C11="Complejo",3,"error")))</f>
@@ -1983,14 +1986,14 @@
       <c r="A12" s="1"/>
       <c r="B12" s="28"/>
       <c r="C12" s="29" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
       <c r="F12" s="7"/>
       <c r="G12" s="30">
         <f>SUM(G8:G11)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -2070,19 +2073,19 @@
     </row>
     <row r="15" ht="27.75" customHeight="1">
       <c r="A15" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="E15" s="20" t="s">
         <v>24</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>27</v>
       </c>
       <c r="F15" s="19" t="s">
         <v>9</v>
@@ -2110,11 +2113,19 @@
     </row>
     <row r="16" ht="27.75" customHeight="1">
       <c r="A16" s="1"/>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
+      <c r="B16" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="36"/>
+      <c r="D16" s="37">
+        <v>3.0</v>
+      </c>
+      <c r="E16" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="38">
+        <v>5.0</v>
+      </c>
       <c r="G16" s="1"/>
       <c r="H16" s="17"/>
       <c r="I16" s="1"/>
@@ -2128,7 +2139,7 @@
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
-      <c r="T16" s="36"/>
+      <c r="T16" s="39"/>
       <c r="U16" s="1"/>
       <c r="V16" s="1"/>
       <c r="W16" s="1"/>
@@ -2138,26 +2149,26 @@
     </row>
     <row r="17" ht="27.75" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" s="21"/>
-      <c r="D17" s="35">
+      <c r="B17" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="41"/>
+      <c r="D17" s="42">
         <v>6.0</v>
       </c>
-      <c r="E17" s="24" t="str">
-        <f t="shared" ref="E17:E19" si="1">IF($D17&gt;0,IF($D17&lt;=3,"Simple",IF(AND($D17&gt;3,$D17&lt;7),"Intermedio",IF($D17&gt;=7,"Complejo","error"))),"-")</f>
+      <c r="E17" s="43" t="str">
+        <f t="shared" ref="E17:E18" si="1">IF($D17&gt;0,IF($D17&lt;=3,"Simple",IF(AND($D17&gt;3,$D17&lt;7),"Intermedio",IF($D17&gt;=7,"Complejo","error"))),"-")</f>
         <v>Intermedio</v>
       </c>
-      <c r="F17" s="24">
-        <f t="shared" ref="F17:F19" si="2">IF($D17&gt;0,IF($D17&lt;=3,5,IF(AND($D17&gt;3,$D17&lt;7),10,IF($D17&gt;=7,15,"error"))),0)</f>
+      <c r="F17" s="43">
+        <f t="shared" ref="F17:F18" si="2">IF($D17&gt;0,IF($D17&lt;=3,5,IF(AND($D17&gt;3,$D17&lt;7),10,IF($D17&gt;=7,15,"error"))),0)</f>
         <v>10</v>
       </c>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
-      <c r="K17" s="36"/>
+      <c r="K17" s="39"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
@@ -2166,7 +2177,7 @@
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
-      <c r="T17" s="36"/>
+      <c r="T17" s="39"/>
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
       <c r="W17" s="1"/>
@@ -2176,26 +2187,26 @@
     </row>
     <row r="18" ht="27.75" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C18" s="21"/>
-      <c r="D18" s="35">
-        <v>2.0</v>
-      </c>
-      <c r="E18" s="24" t="str">
+      <c r="B18" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="44"/>
+      <c r="D18" s="45">
+        <v>8.0</v>
+      </c>
+      <c r="E18" s="43" t="str">
         <f t="shared" si="1"/>
-        <v>Simple</v>
-      </c>
-      <c r="F18" s="24">
+        <v>Complejo</v>
+      </c>
+      <c r="F18" s="43">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
-      <c r="K18" s="36"/>
+      <c r="K18" s="39"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
@@ -2204,7 +2215,7 @@
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
-      <c r="T18" s="36"/>
+      <c r="T18" s="39"/>
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
@@ -2214,26 +2225,24 @@
     </row>
     <row r="19" ht="27.75" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" s="37"/>
-      <c r="D19" s="38">
-        <v>6.0</v>
-      </c>
-      <c r="E19" s="24" t="str">
-        <f t="shared" si="1"/>
-        <v>Intermedio</v>
-      </c>
-      <c r="F19" s="24">
-        <f t="shared" si="2"/>
-        <v>10</v>
+      <c r="B19" s="40" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="44"/>
+      <c r="D19" s="45">
+        <v>3.0</v>
+      </c>
+      <c r="E19" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="F19" s="43">
+        <v>5.0</v>
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
-      <c r="K19" s="36"/>
+      <c r="K19" s="39"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
@@ -2242,7 +2251,7 @@
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
-      <c r="T19" s="36"/>
+      <c r="T19" s="39"/>
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
       <c r="W19" s="1"/>
@@ -2252,24 +2261,26 @@
     </row>
     <row r="20" ht="27.75" customHeight="1">
       <c r="A20" s="1"/>
-      <c r="B20" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" s="37"/>
-      <c r="D20" s="38">
-        <v>3.0</v>
-      </c>
-      <c r="E20" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="F20" s="24">
-        <v>5.0</v>
+      <c r="B20" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="44"/>
+      <c r="D20" s="45">
+        <v>10.0</v>
+      </c>
+      <c r="E20" s="43" t="str">
+        <f>IF($D20&gt;0,IF($D20&lt;=3,"Simple",IF(AND($D20&gt;3,$D20&lt;7),"Intermedio",IF($D20&gt;=7,"Complejo","error"))),"-")</f>
+        <v>Complejo</v>
+      </c>
+      <c r="F20" s="43">
+        <f>IF($D20&gt;0,IF($D20&lt;=3,5,IF(AND($D20&gt;3,$D20&lt;7),10,IF($D20&gt;=7,15,"error"))),0)</f>
+        <v>15</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
-      <c r="K20" s="36"/>
+      <c r="K20" s="39"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
@@ -2278,7 +2289,7 @@
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
-      <c r="T20" s="36"/>
+      <c r="T20" s="39"/>
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
       <c r="W20" s="1"/>
@@ -2288,26 +2299,24 @@
     </row>
     <row r="21" ht="27.75" customHeight="1">
       <c r="A21" s="1"/>
-      <c r="B21" s="21" t="s">
+      <c r="B21" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="44"/>
+      <c r="D21" s="45">
+        <v>4.0</v>
+      </c>
+      <c r="E21" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="C21" s="37"/>
-      <c r="D21" s="38">
-        <v>3.0</v>
-      </c>
-      <c r="E21" s="24" t="str">
-        <f t="shared" ref="E21:E23" si="3">IF($D21&gt;0,IF($D21&lt;=3,"Simple",IF(AND($D21&gt;3,$D21&lt;7),"Intermedio",IF($D21&gt;=7,"Complejo","error"))),"-")</f>
-        <v>Simple</v>
-      </c>
-      <c r="F21" s="24">
-        <f t="shared" ref="F21:F23" si="4">IF($D21&gt;0,IF($D21&lt;=3,5,IF(AND($D21&gt;3,$D21&lt;7),10,IF($D21&gt;=7,15,"error"))),0)</f>
-        <v>5</v>
+      <c r="F21" s="43">
+        <v>10.0</v>
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
-      <c r="K21" s="36"/>
+      <c r="K21" s="39"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
@@ -2316,7 +2325,7 @@
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
-      <c r="T21" s="36"/>
+      <c r="T21" s="39"/>
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
@@ -2326,26 +2335,26 @@
     </row>
     <row r="22" ht="27.75" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="37"/>
-      <c r="D22" s="38">
-        <v>3.0</v>
-      </c>
-      <c r="E22" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v>Simple</v>
-      </c>
-      <c r="F22" s="24">
-        <f t="shared" si="4"/>
-        <v>5</v>
+      <c r="C22" s="44"/>
+      <c r="D22" s="45">
+        <v>4.0</v>
+      </c>
+      <c r="E22" s="43" t="str">
+        <f t="shared" ref="E22:E26" si="3">IF($D22&gt;0,IF($D22&lt;=3,"Simple",IF(AND($D22&gt;3,$D22&lt;7),"Intermedio",IF($D22&gt;=7,"Complejo","error"))),"-")</f>
+        <v>Intermedio</v>
+      </c>
+      <c r="F22" s="43">
+        <f t="shared" ref="F22:F26" si="4">IF($D22&gt;0,IF($D22&lt;=3,5,IF(AND($D22&gt;3,$D22&lt;7),10,IF($D22&gt;=7,15,"error"))),0)</f>
+        <v>10</v>
       </c>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
-      <c r="K22" s="36"/>
+      <c r="K22" s="39"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
@@ -2354,7 +2363,7 @@
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
-      <c r="T22" s="36"/>
+      <c r="T22" s="39"/>
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
       <c r="W22" s="1"/>
@@ -2364,26 +2373,26 @@
     </row>
     <row r="23" ht="27.75" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="21" t="s">
+      <c r="B23" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="C23" s="37"/>
-      <c r="D23" s="38">
-        <v>10.0</v>
-      </c>
-      <c r="E23" s="24" t="str">
+      <c r="C23" s="44"/>
+      <c r="D23" s="45">
+        <v>3.0</v>
+      </c>
+      <c r="E23" s="43" t="str">
         <f t="shared" si="3"/>
-        <v>Complejo</v>
-      </c>
-      <c r="F23" s="24">
+        <v>Simple</v>
+      </c>
+      <c r="F23" s="43">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
-      <c r="K23" s="36"/>
+      <c r="K23" s="39"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
@@ -2392,7 +2401,7 @@
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
-      <c r="T23" s="36"/>
+      <c r="T23" s="39"/>
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
       <c r="W23" s="1"/>
@@ -2402,24 +2411,26 @@
     </row>
     <row r="24" ht="27.75" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="C24" s="37"/>
-      <c r="D24" s="38">
-        <v>4.0</v>
-      </c>
-      <c r="E24" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="F24" s="24">
-        <v>10.0</v>
+      <c r="C24" s="44"/>
+      <c r="D24" s="45">
+        <v>3.0</v>
+      </c>
+      <c r="E24" s="43" t="str">
+        <f t="shared" si="3"/>
+        <v>Simple</v>
+      </c>
+      <c r="F24" s="43">
+        <f t="shared" si="4"/>
+        <v>5</v>
       </c>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
-      <c r="K24" s="36"/>
+      <c r="K24" s="39"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
@@ -2428,7 +2439,7 @@
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
-      <c r="T24" s="36"/>
+      <c r="T24" s="39"/>
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
       <c r="W24" s="1"/>
@@ -2438,26 +2449,26 @@
     </row>
     <row r="25" ht="27.75" customHeight="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="C25" s="37"/>
-      <c r="D25" s="38">
+      <c r="B25" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" s="41"/>
+      <c r="D25" s="45">
         <v>4.0</v>
       </c>
-      <c r="E25" s="24" t="str">
-        <f t="shared" ref="E25:E29" si="5">IF($D25&gt;0,IF($D25&lt;=3,"Simple",IF(AND($D25&gt;3,$D25&lt;7),"Intermedio",IF($D25&gt;=7,"Complejo","error"))),"-")</f>
+      <c r="E25" s="43" t="str">
+        <f t="shared" si="3"/>
         <v>Intermedio</v>
       </c>
-      <c r="F25" s="24">
-        <f t="shared" ref="F25:F29" si="6">IF($D25&gt;0,IF($D25&lt;=3,5,IF(AND($D25&gt;3,$D25&lt;7),10,IF($D25&gt;=7,15,"error"))),0)</f>
+      <c r="F25" s="43">
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
-      <c r="K25" s="36"/>
+      <c r="K25" s="39"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
@@ -2466,7 +2477,7 @@
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
-      <c r="T25" s="36"/>
+      <c r="T25" s="39"/>
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
       <c r="W25" s="1"/>
@@ -2476,26 +2487,26 @@
     </row>
     <row r="26" ht="27.75" customHeight="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="C26" s="37"/>
-      <c r="D26" s="38">
+      <c r="B26" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" s="44"/>
+      <c r="D26" s="45">
         <v>3.0</v>
       </c>
-      <c r="E26" s="24" t="str">
-        <f t="shared" si="5"/>
+      <c r="E26" s="43" t="str">
+        <f t="shared" si="3"/>
         <v>Simple</v>
       </c>
-      <c r="F26" s="24">
-        <f t="shared" si="6"/>
+      <c r="F26" s="43">
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
-      <c r="K26" s="36"/>
+      <c r="K26" s="39"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
@@ -2504,7 +2515,7 @@
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
-      <c r="T26" s="36"/>
+      <c r="T26" s="39"/>
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
       <c r="W26" s="1"/>
@@ -2514,26 +2525,16 @@
     </row>
     <row r="27" ht="27.75" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="C27" s="37"/>
-      <c r="D27" s="38">
-        <v>3.0</v>
-      </c>
-      <c r="E27" s="24" t="str">
-        <f t="shared" si="5"/>
-        <v>Simple</v>
-      </c>
-      <c r="F27" s="24">
-        <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
+      <c r="B27" s="21"/>
+      <c r="C27" s="46"/>
+      <c r="D27" s="47"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="24"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
-      <c r="K27" s="36"/>
+      <c r="K27" s="39"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
@@ -2542,7 +2543,7 @@
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
-      <c r="T27" s="36"/>
+      <c r="T27" s="39"/>
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
       <c r="W27" s="1"/>
@@ -2552,26 +2553,16 @@
     </row>
     <row r="28" ht="27.75" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="21" t="s">
-        <v>40</v>
-      </c>
+      <c r="B28" s="21"/>
       <c r="C28" s="21"/>
-      <c r="D28" s="38">
-        <v>4.0</v>
-      </c>
-      <c r="E28" s="24" t="str">
-        <f t="shared" si="5"/>
-        <v>Intermedio</v>
-      </c>
-      <c r="F28" s="24">
-        <f t="shared" si="6"/>
-        <v>10</v>
-      </c>
+      <c r="D28" s="47"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
-      <c r="K28" s="36"/>
+      <c r="K28" s="39"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
@@ -2580,7 +2571,7 @@
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
-      <c r="T28" s="36"/>
+      <c r="T28" s="39"/>
       <c r="U28" s="1"/>
       <c r="V28" s="1"/>
       <c r="W28" s="1"/>
@@ -2590,26 +2581,16 @@
     </row>
     <row r="29" ht="27.75" customHeight="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="C29" s="37"/>
-      <c r="D29" s="38">
-        <v>3.0</v>
-      </c>
-      <c r="E29" s="24" t="str">
-        <f t="shared" si="5"/>
-        <v>Simple</v>
-      </c>
-      <c r="F29" s="24">
-        <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
+      <c r="B29" s="21"/>
+      <c r="C29" s="46"/>
+      <c r="D29" s="47"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="24"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
-      <c r="K29" s="36"/>
+      <c r="K29" s="39"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
@@ -2618,7 +2599,7 @@
       <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
-      <c r="T29" s="36"/>
+      <c r="T29" s="39"/>
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
       <c r="W29" s="1"/>
@@ -2628,21 +2609,21 @@
     </row>
     <row r="30" ht="27.75" customHeight="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="39"/>
-      <c r="C30" s="40" t="s">
-        <v>42</v>
-      </c>
-      <c r="D30" s="41"/>
-      <c r="E30" s="42"/>
-      <c r="F30" s="43">
+      <c r="B30" s="48"/>
+      <c r="C30" s="49" t="s">
+        <v>38</v>
+      </c>
+      <c r="D30" s="50"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="52">
         <f>SUM(F16:F29)</f>
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
-      <c r="K30" s="36"/>
+      <c r="K30" s="39"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
@@ -2651,7 +2632,7 @@
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
-      <c r="T30" s="36"/>
+      <c r="T30" s="39"/>
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
       <c r="W30" s="1"/>
@@ -2670,7 +2651,7 @@
       <c r="H31" s="18"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
-      <c r="K31" s="36"/>
+      <c r="K31" s="39"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
@@ -2717,17 +2698,17 @@
     </row>
     <row r="33" ht="27.75" customHeight="1">
       <c r="A33" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="B33" s="44"/>
+        <v>39</v>
+      </c>
+      <c r="B33" s="53"/>
       <c r="C33" s="29" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D33" s="6"/>
       <c r="E33" s="7"/>
       <c r="F33" s="30">
         <f>G12+F30</f>
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
@@ -2808,25 +2789,25 @@
     </row>
     <row r="36" ht="27.75" customHeight="1">
       <c r="A36" s="18" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C36" s="20" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D36" s="19" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E36" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F36" s="19" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G36" s="19" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -2850,27 +2831,27 @@
     </row>
     <row r="37" ht="27.75" customHeight="1">
       <c r="A37" s="1"/>
-      <c r="B37" s="45" t="s">
-        <v>51</v>
-      </c>
-      <c r="C37" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D37" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="E37" s="47">
+      <c r="B37" s="54" t="s">
+        <v>47</v>
+      </c>
+      <c r="C37" s="54" t="s">
+        <v>48</v>
+      </c>
+      <c r="D37" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="E37" s="56">
         <v>2.0</v>
       </c>
       <c r="F37" s="25">
         <v>0.0</v>
       </c>
-      <c r="G37" s="48">
-        <f t="shared" ref="G37:G49" si="7">E37*F37</f>
+      <c r="G37" s="57">
+        <f t="shared" ref="G37:G49" si="5">E37*F37</f>
         <v>0</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I37" s="18"/>
       <c r="J37" s="18"/>
@@ -2893,27 +2874,27 @@
     </row>
     <row r="38" ht="27.75" customHeight="1">
       <c r="A38" s="1"/>
-      <c r="B38" s="45" t="s">
-        <v>55</v>
-      </c>
-      <c r="C38" s="45" t="s">
+      <c r="B38" s="54" t="s">
+        <v>51</v>
+      </c>
+      <c r="C38" s="54" t="s">
+        <v>48</v>
+      </c>
+      <c r="D38" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="49" t="s">
-        <v>56</v>
-      </c>
-      <c r="E38" s="48">
+      <c r="E38" s="57">
         <v>2.0</v>
       </c>
       <c r="F38" s="25">
         <v>5.0</v>
       </c>
-      <c r="G38" s="48">
-        <f t="shared" si="7"/>
+      <c r="G38" s="57">
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="H38" s="50" t="s">
-        <v>57</v>
+      <c r="H38" s="59" t="s">
+        <v>53</v>
       </c>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
@@ -2936,21 +2917,21 @@
     </row>
     <row r="39" ht="27.0" customHeight="1">
       <c r="A39" s="1"/>
-      <c r="B39" s="45" t="s">
-        <v>58</v>
-      </c>
-      <c r="C39" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D39" s="49"/>
-      <c r="E39" s="48">
+      <c r="B39" s="54" t="s">
+        <v>54</v>
+      </c>
+      <c r="C39" s="54" t="s">
+        <v>48</v>
+      </c>
+      <c r="D39" s="58"/>
+      <c r="E39" s="57">
         <v>1.0</v>
       </c>
       <c r="F39" s="25">
         <v>5.0</v>
       </c>
-      <c r="G39" s="48">
-        <f t="shared" si="7"/>
+      <c r="G39" s="57">
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="H39" s="1"/>
@@ -2975,23 +2956,23 @@
     </row>
     <row r="40" ht="27.75" customHeight="1">
       <c r="A40" s="1"/>
-      <c r="B40" s="45" t="s">
-        <v>59</v>
-      </c>
-      <c r="C40" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D40" s="46" t="s">
-        <v>60</v>
-      </c>
-      <c r="E40" s="48">
+      <c r="B40" s="54" t="s">
+        <v>55</v>
+      </c>
+      <c r="C40" s="54" t="s">
+        <v>48</v>
+      </c>
+      <c r="D40" s="55" t="s">
+        <v>56</v>
+      </c>
+      <c r="E40" s="57">
         <v>1.0</v>
       </c>
       <c r="F40" s="25">
         <v>3.0</v>
       </c>
-      <c r="G40" s="48">
-        <f t="shared" si="7"/>
+      <c r="G40" s="57">
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="H40" s="1"/>
@@ -3016,23 +2997,23 @@
     </row>
     <row r="41" ht="30.75" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="45" t="s">
-        <v>61</v>
-      </c>
-      <c r="C41" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D41" s="46" t="s">
-        <v>62</v>
-      </c>
-      <c r="E41" s="47">
+      <c r="B41" s="54" t="s">
+        <v>57</v>
+      </c>
+      <c r="C41" s="54" t="s">
+        <v>48</v>
+      </c>
+      <c r="D41" s="55" t="s">
+        <v>58</v>
+      </c>
+      <c r="E41" s="56">
         <v>1.0</v>
       </c>
       <c r="F41" s="25">
         <v>0.0</v>
       </c>
-      <c r="G41" s="48">
-        <f t="shared" si="7"/>
+      <c r="G41" s="57">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H41" s="1"/>
@@ -3057,23 +3038,23 @@
     </row>
     <row r="42" ht="27.75" customHeight="1">
       <c r="A42" s="1"/>
-      <c r="B42" s="45" t="s">
-        <v>63</v>
-      </c>
-      <c r="C42" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D42" s="49" t="s">
-        <v>64</v>
-      </c>
-      <c r="E42" s="47">
+      <c r="B42" s="54" t="s">
+        <v>59</v>
+      </c>
+      <c r="C42" s="54" t="s">
+        <v>48</v>
+      </c>
+      <c r="D42" s="58" t="s">
+        <v>60</v>
+      </c>
+      <c r="E42" s="56">
         <v>0.5</v>
       </c>
       <c r="F42" s="25">
         <v>3.0</v>
       </c>
-      <c r="G42" s="48">
-        <f t="shared" si="7"/>
+      <c r="G42" s="57">
+        <f t="shared" si="5"/>
         <v>1.5</v>
       </c>
       <c r="H42" s="1"/>
@@ -3098,23 +3079,23 @@
     </row>
     <row r="43" ht="27.75" customHeight="1">
       <c r="A43" s="1"/>
-      <c r="B43" s="45" t="s">
-        <v>65</v>
-      </c>
-      <c r="C43" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D43" s="49" t="s">
-        <v>66</v>
-      </c>
-      <c r="E43" s="47">
+      <c r="B43" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="C43" s="54" t="s">
+        <v>48</v>
+      </c>
+      <c r="D43" s="58" t="s">
+        <v>62</v>
+      </c>
+      <c r="E43" s="56">
         <v>0.5</v>
       </c>
       <c r="F43" s="25">
         <v>5.0</v>
       </c>
-      <c r="G43" s="48">
-        <f t="shared" si="7"/>
+      <c r="G43" s="57">
+        <f t="shared" si="5"/>
         <v>2.5</v>
       </c>
       <c r="H43" s="1"/>
@@ -3139,23 +3120,23 @@
     </row>
     <row r="44" ht="27.75" customHeight="1">
       <c r="A44" s="1"/>
-      <c r="B44" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="C44" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D44" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="E44" s="47">
+      <c r="B44" s="54" t="s">
+        <v>63</v>
+      </c>
+      <c r="C44" s="54" t="s">
+        <v>48</v>
+      </c>
+      <c r="D44" s="58" t="s">
+        <v>64</v>
+      </c>
+      <c r="E44" s="56">
         <v>2.0</v>
       </c>
       <c r="F44" s="25">
         <v>3.0</v>
       </c>
-      <c r="G44" s="48">
-        <f t="shared" si="7"/>
+      <c r="G44" s="57">
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="H44" s="1"/>
@@ -3180,23 +3161,23 @@
     </row>
     <row r="45" ht="27.75" customHeight="1">
       <c r="A45" s="1"/>
-      <c r="B45" s="45" t="s">
-        <v>69</v>
-      </c>
-      <c r="C45" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D45" s="46" t="s">
-        <v>70</v>
-      </c>
-      <c r="E45" s="47">
+      <c r="B45" s="54" t="s">
+        <v>65</v>
+      </c>
+      <c r="C45" s="54" t="s">
+        <v>48</v>
+      </c>
+      <c r="D45" s="55" t="s">
+        <v>66</v>
+      </c>
+      <c r="E45" s="56">
         <v>1.0</v>
       </c>
       <c r="F45" s="25">
         <v>0.0</v>
       </c>
-      <c r="G45" s="48">
-        <f t="shared" si="7"/>
+      <c r="G45" s="57">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H45" s="1"/>
@@ -3221,21 +3202,21 @@
     </row>
     <row r="46" ht="27.75" customHeight="1">
       <c r="A46" s="1"/>
-      <c r="B46" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="C46" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D46" s="46"/>
-      <c r="E46" s="47">
+      <c r="B46" s="54" t="s">
+        <v>67</v>
+      </c>
+      <c r="C46" s="54" t="s">
+        <v>48</v>
+      </c>
+      <c r="D46" s="55"/>
+      <c r="E46" s="56">
         <v>1.0</v>
       </c>
       <c r="F46" s="25">
         <v>5.0</v>
       </c>
-      <c r="G46" s="48">
-        <f t="shared" si="7"/>
+      <c r="G46" s="57">
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="H46" s="1"/>
@@ -3260,23 +3241,23 @@
     </row>
     <row r="47" ht="27.75" customHeight="1">
       <c r="A47" s="1"/>
-      <c r="B47" s="45" t="s">
-        <v>72</v>
-      </c>
-      <c r="C47" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D47" s="46" t="s">
-        <v>73</v>
-      </c>
-      <c r="E47" s="48">
+      <c r="B47" s="54" t="s">
+        <v>68</v>
+      </c>
+      <c r="C47" s="54" t="s">
+        <v>48</v>
+      </c>
+      <c r="D47" s="55" t="s">
+        <v>69</v>
+      </c>
+      <c r="E47" s="57">
         <v>1.0</v>
       </c>
       <c r="F47" s="25">
         <v>5.0</v>
       </c>
-      <c r="G47" s="48">
-        <f t="shared" si="7"/>
+      <c r="G47" s="57">
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="H47" s="1"/>
@@ -3301,23 +3282,23 @@
     </row>
     <row r="48" ht="30.75" customHeight="1">
       <c r="A48" s="1"/>
-      <c r="B48" s="45" t="s">
-        <v>74</v>
-      </c>
-      <c r="C48" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D48" s="46" t="s">
-        <v>75</v>
-      </c>
-      <c r="E48" s="48">
+      <c r="B48" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="C48" s="54" t="s">
+        <v>48</v>
+      </c>
+      <c r="D48" s="55" t="s">
+        <v>71</v>
+      </c>
+      <c r="E48" s="57">
         <v>1.0</v>
       </c>
       <c r="F48" s="25">
         <v>5.0</v>
       </c>
-      <c r="G48" s="48">
-        <f t="shared" si="7"/>
+      <c r="G48" s="57">
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="H48" s="1"/>
@@ -3342,23 +3323,23 @@
     </row>
     <row r="49" ht="31.5" customHeight="1">
       <c r="A49" s="1"/>
-      <c r="B49" s="45" t="s">
-        <v>76</v>
-      </c>
-      <c r="C49" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="D49" s="46" t="s">
-        <v>77</v>
-      </c>
-      <c r="E49" s="47">
+      <c r="B49" s="54" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="54" t="s">
+        <v>48</v>
+      </c>
+      <c r="D49" s="55" t="s">
+        <v>73</v>
+      </c>
+      <c r="E49" s="56">
         <v>1.0</v>
       </c>
       <c r="F49" s="25">
         <v>4.0</v>
       </c>
-      <c r="G49" s="48">
-        <f t="shared" si="7"/>
+      <c r="G49" s="57">
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="H49" s="1"/>
@@ -3384,13 +3365,13 @@
     <row r="50" ht="30.75" customHeight="1">
       <c r="A50" s="1"/>
       <c r="B50" s="29" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
       <c r="F50" s="7"/>
-      <c r="G50" s="51">
+      <c r="G50" s="60">
         <f>SUM(G37:G49)</f>
         <v>47</v>
       </c>
@@ -3417,13 +3398,13 @@
     <row r="51" ht="27.75" customHeight="1">
       <c r="A51" s="1"/>
       <c r="B51" s="29" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C51" s="6"/>
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
       <c r="F51" s="7"/>
-      <c r="G51" s="43">
+      <c r="G51" s="52">
         <f>0.6+(0.01*G50)</f>
         <v>1.07</v>
       </c>
@@ -3477,12 +3458,12 @@
     </row>
     <row r="53" ht="27.75" customHeight="1">
       <c r="A53" s="1"/>
-      <c r="B53" s="52"/>
-      <c r="C53" s="52"/>
-      <c r="D53" s="53"/>
-      <c r="E53" s="52"/>
-      <c r="F53" s="52"/>
-      <c r="G53" s="52"/>
+      <c r="B53" s="61"/>
+      <c r="C53" s="61"/>
+      <c r="D53" s="62"/>
+      <c r="E53" s="61"/>
+      <c r="F53" s="61"/>
+      <c r="G53" s="61"/>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
@@ -3505,25 +3486,25 @@
     </row>
     <row r="54" ht="27.75" customHeight="1">
       <c r="A54" s="18" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B54" s="20" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C54" s="20" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D54" s="19" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E54" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F54" s="19" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G54" s="19" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
@@ -3547,27 +3528,27 @@
     </row>
     <row r="55" ht="64.5" customHeight="1">
       <c r="A55" s="1"/>
-      <c r="B55" s="54" t="s">
-        <v>84</v>
-      </c>
-      <c r="C55" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="D55" s="49" t="s">
-        <v>86</v>
-      </c>
-      <c r="E55" s="47">
+      <c r="B55" s="63" t="s">
+        <v>80</v>
+      </c>
+      <c r="C55" s="54" t="s">
+        <v>81</v>
+      </c>
+      <c r="D55" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="E55" s="56">
         <v>1.5</v>
       </c>
-      <c r="F55" s="55">
+      <c r="F55" s="64">
         <v>3.0</v>
       </c>
-      <c r="G55" s="48">
-        <f t="shared" ref="G55:G62" si="8">E55*F55</f>
+      <c r="G55" s="57">
+        <f t="shared" ref="G55:G62" si="6">E55*F55</f>
         <v>4.5</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="I55" s="18"/>
       <c r="J55" s="18"/>
@@ -3590,27 +3571,27 @@
     </row>
     <row r="56" ht="51.0" customHeight="1">
       <c r="A56" s="1"/>
-      <c r="B56" s="54" t="s">
-        <v>88</v>
-      </c>
-      <c r="C56" s="45" t="s">
+      <c r="B56" s="63" t="s">
+        <v>84</v>
+      </c>
+      <c r="C56" s="54" t="s">
+        <v>81</v>
+      </c>
+      <c r="D56" s="58" t="s">
         <v>85</v>
       </c>
-      <c r="D56" s="49" t="s">
-        <v>89</v>
-      </c>
-      <c r="E56" s="47">
+      <c r="E56" s="56">
         <v>0.5</v>
       </c>
-      <c r="F56" s="55">
+      <c r="F56" s="64">
         <v>3.0</v>
       </c>
-      <c r="G56" s="48">
-        <f t="shared" si="8"/>
+      <c r="G56" s="57">
+        <f t="shared" si="6"/>
         <v>1.5</v>
       </c>
-      <c r="H56" s="50" t="s">
-        <v>57</v>
+      <c r="H56" s="59" t="s">
+        <v>53</v>
       </c>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
@@ -3633,23 +3614,23 @@
     </row>
     <row r="57" ht="48.75" customHeight="1">
       <c r="A57" s="1"/>
-      <c r="B57" s="54" t="s">
-        <v>90</v>
-      </c>
-      <c r="C57" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="D57" s="49" t="s">
-        <v>91</v>
-      </c>
-      <c r="E57" s="47">
+      <c r="B57" s="63" t="s">
+        <v>86</v>
+      </c>
+      <c r="C57" s="54" t="s">
+        <v>81</v>
+      </c>
+      <c r="D57" s="58" t="s">
+        <v>87</v>
+      </c>
+      <c r="E57" s="56">
         <v>1.0</v>
       </c>
-      <c r="F57" s="55">
+      <c r="F57" s="64">
         <v>3.0</v>
       </c>
-      <c r="G57" s="48">
-        <f t="shared" si="8"/>
+      <c r="G57" s="57">
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="H57" s="1"/>
@@ -3674,23 +3655,23 @@
     </row>
     <row r="58" ht="46.5" customHeight="1">
       <c r="A58" s="1"/>
-      <c r="B58" s="54" t="s">
-        <v>92</v>
-      </c>
-      <c r="C58" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="D58" s="49" t="s">
-        <v>93</v>
-      </c>
-      <c r="E58" s="47">
+      <c r="B58" s="63" t="s">
+        <v>88</v>
+      </c>
+      <c r="C58" s="54" t="s">
+        <v>81</v>
+      </c>
+      <c r="D58" s="58" t="s">
+        <v>89</v>
+      </c>
+      <c r="E58" s="56">
         <v>0.5</v>
       </c>
-      <c r="F58" s="55">
+      <c r="F58" s="64">
         <v>2.0</v>
       </c>
-      <c r="G58" s="48">
-        <f t="shared" si="8"/>
+      <c r="G58" s="57">
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="H58" s="1"/>
@@ -3715,23 +3696,23 @@
     </row>
     <row r="59" ht="37.5" customHeight="1">
       <c r="A59" s="1"/>
-      <c r="B59" s="54" t="s">
-        <v>94</v>
-      </c>
-      <c r="C59" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="D59" s="46" t="s">
-        <v>96</v>
-      </c>
-      <c r="E59" s="47">
+      <c r="B59" s="63" t="s">
+        <v>90</v>
+      </c>
+      <c r="C59" s="54" t="s">
+        <v>91</v>
+      </c>
+      <c r="D59" s="55" t="s">
+        <v>92</v>
+      </c>
+      <c r="E59" s="56">
         <v>1.0</v>
       </c>
-      <c r="F59" s="55">
+      <c r="F59" s="64">
         <v>3.0</v>
       </c>
-      <c r="G59" s="48">
-        <f t="shared" si="8"/>
+      <c r="G59" s="57">
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="H59" s="1"/>
@@ -3756,23 +3737,23 @@
     </row>
     <row r="60" ht="43.5" customHeight="1">
       <c r="A60" s="1"/>
-      <c r="B60" s="54" t="s">
-        <v>97</v>
-      </c>
-      <c r="C60" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="D60" s="46" t="s">
-        <v>99</v>
-      </c>
-      <c r="E60" s="47">
+      <c r="B60" s="63" t="s">
+        <v>93</v>
+      </c>
+      <c r="C60" s="54" t="s">
+        <v>94</v>
+      </c>
+      <c r="D60" s="55" t="s">
+        <v>95</v>
+      </c>
+      <c r="E60" s="56">
         <v>2.0</v>
       </c>
-      <c r="F60" s="55">
+      <c r="F60" s="64">
         <v>4.0</v>
       </c>
-      <c r="G60" s="48">
-        <f t="shared" si="8"/>
+      <c r="G60" s="57">
+        <f t="shared" si="6"/>
         <v>8</v>
       </c>
       <c r="H60" s="1"/>
@@ -3797,23 +3778,23 @@
     </row>
     <row r="61" ht="71.25" customHeight="1">
       <c r="A61" s="1"/>
-      <c r="B61" s="54" t="s">
-        <v>100</v>
-      </c>
-      <c r="C61" s="45" t="s">
-        <v>101</v>
-      </c>
-      <c r="D61" s="56" t="s">
-        <v>102</v>
-      </c>
-      <c r="E61" s="47">
+      <c r="B61" s="63" t="s">
+        <v>96</v>
+      </c>
+      <c r="C61" s="54" t="s">
+        <v>97</v>
+      </c>
+      <c r="D61" s="65" t="s">
+        <v>98</v>
+      </c>
+      <c r="E61" s="56">
         <v>-1.0</v>
       </c>
-      <c r="F61" s="55">
+      <c r="F61" s="64">
         <v>2.0</v>
       </c>
-      <c r="G61" s="48">
-        <f t="shared" si="8"/>
+      <c r="G61" s="57">
+        <f t="shared" si="6"/>
         <v>-2</v>
       </c>
       <c r="H61" s="1"/>
@@ -3838,23 +3819,23 @@
     </row>
     <row r="62" ht="62.25" customHeight="1">
       <c r="A62" s="1"/>
-      <c r="B62" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="C62" s="45" t="s">
-        <v>104</v>
-      </c>
-      <c r="D62" s="56" t="s">
-        <v>105</v>
-      </c>
-      <c r="E62" s="47">
+      <c r="B62" s="63" t="s">
+        <v>99</v>
+      </c>
+      <c r="C62" s="54" t="s">
+        <v>100</v>
+      </c>
+      <c r="D62" s="65" t="s">
+        <v>101</v>
+      </c>
+      <c r="E62" s="56">
         <v>-1.0</v>
       </c>
-      <c r="F62" s="55">
+      <c r="F62" s="64">
         <v>4.0</v>
       </c>
-      <c r="G62" s="48">
-        <f t="shared" si="8"/>
+      <c r="G62" s="57">
+        <f t="shared" si="6"/>
         <v>-4</v>
       </c>
       <c r="H62" s="1"/>
@@ -3880,7 +3861,7 @@
     <row r="63" ht="38.25" customHeight="1">
       <c r="A63" s="1"/>
       <c r="B63" s="29" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C63" s="6"/>
       <c r="D63" s="6"/>
@@ -3913,7 +3894,7 @@
     <row r="64" ht="27.75" customHeight="1">
       <c r="A64" s="1"/>
       <c r="B64" s="29" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="6"/>
@@ -3946,11 +3927,11 @@
     <row r="65" ht="27.75" customHeight="1">
       <c r="A65" s="1"/>
       <c r="B65" s="29"/>
-      <c r="C65" s="57"/>
-      <c r="D65" s="58"/>
-      <c r="E65" s="57"/>
-      <c r="F65" s="59" t="s">
-        <v>108</v>
+      <c r="C65" s="66"/>
+      <c r="D65" s="67"/>
+      <c r="E65" s="66"/>
+      <c r="F65" s="68" t="s">
+        <v>104</v>
       </c>
       <c r="G65" s="19">
         <f>COUNTIF($F$55:$F$60,"&lt;3")+COUNTIF($F$61:$F$62,"&gt;3")</f>
@@ -4034,18 +4015,18 @@
     </row>
     <row r="68" ht="27.75" customHeight="1">
       <c r="A68" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="B68" s="60" t="s">
-        <v>110</v>
+        <v>105</v>
+      </c>
+      <c r="B68" s="69" t="s">
+        <v>106</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="6"/>
       <c r="E68" s="6"/>
       <c r="F68" s="7"/>
-      <c r="G68" s="61">
+      <c r="G68" s="70">
         <f>F33*G51*G64</f>
-        <v>105.716</v>
+        <v>99.617</v>
       </c>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
@@ -4124,22 +4105,22 @@
       <c r="Z70" s="1"/>
     </row>
     <row r="71" ht="27.75" customHeight="1">
-      <c r="A71" s="62" t="s">
-        <v>111</v>
+      <c r="A71" s="71" t="s">
+        <v>107</v>
       </c>
       <c r="B71" s="20" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C71" s="20" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D71" s="20" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="1"/>
       <c r="G71" s="20" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
@@ -4163,20 +4144,20 @@
     </row>
     <row r="72" ht="31.5" customHeight="1">
       <c r="A72" s="1"/>
-      <c r="B72" s="63">
+      <c r="B72" s="72">
         <v>20.0</v>
       </c>
-      <c r="C72" s="63">
+      <c r="C72" s="72">
         <f>IF($G$65&gt;=5,36,IF(AND(G$65&gt;2,$G$65&lt;=4),28, IF(AND($G$65&gt;=0,$G$65&lt;=2),20,"error")))</f>
         <v>20</v>
       </c>
-      <c r="D72" s="64">
+      <c r="D72" s="73">
         <f>IF($G$65&gt;=5,$G$72*(36/20),IF(AND($G$65&gt;2,$G$65&lt;=4),$G$72*(28/20), IF(AND($G$65&gt;=0,$G$65&lt;=2),$G$72,"error")))</f>
         <v>2</v>
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="1"/>
-      <c r="G72" s="65">
+      <c r="G72" s="74">
         <v>2.0</v>
       </c>
       <c r="H72" s="1"/>
@@ -4201,8 +4182,8 @@
     </row>
     <row r="73" ht="27.75" customHeight="1">
       <c r="A73" s="1"/>
-      <c r="B73" s="66" t="s">
-        <v>116</v>
+      <c r="B73" s="75" t="s">
+        <v>112</v>
       </c>
       <c r="C73" s="6"/>
       <c r="D73" s="7"/>
@@ -4230,20 +4211,20 @@
       <c r="Z73" s="1"/>
     </row>
     <row r="74" ht="27.75" customHeight="1">
-      <c r="A74" s="67" t="s">
-        <v>117</v>
-      </c>
-      <c r="B74" s="63">
-        <f t="shared" ref="B74:D74" si="9">$G$68*B72</f>
-        <v>2114.32</v>
-      </c>
-      <c r="C74" s="63">
-        <f t="shared" si="9"/>
-        <v>2114.32</v>
-      </c>
-      <c r="D74" s="63">
-        <f t="shared" si="9"/>
-        <v>211.432</v>
+      <c r="A74" s="76" t="s">
+        <v>113</v>
+      </c>
+      <c r="B74" s="72">
+        <f t="shared" ref="B74:D74" si="7">$G$68*B72</f>
+        <v>1992.34</v>
+      </c>
+      <c r="C74" s="72">
+        <f t="shared" si="7"/>
+        <v>1992.34</v>
+      </c>
+      <c r="D74" s="72">
+        <f t="shared" si="7"/>
+        <v>199.234</v>
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="1"/>
@@ -4269,20 +4250,20 @@
       <c r="Z74" s="1"/>
     </row>
     <row r="75" ht="27.75" customHeight="1">
-      <c r="A75" s="67" t="s">
-        <v>118</v>
-      </c>
-      <c r="B75" s="68">
-        <f t="shared" ref="B75:C75" si="10">B74/(22*8)</f>
-        <v>12.01318182</v>
-      </c>
-      <c r="C75" s="68">
-        <f t="shared" si="10"/>
-        <v>12.01318182</v>
-      </c>
-      <c r="D75" s="69">
+      <c r="A75" s="76" t="s">
+        <v>114</v>
+      </c>
+      <c r="B75" s="77">
+        <f t="shared" ref="B75:C75" si="8">B74/(22*8)</f>
+        <v>11.32011364</v>
+      </c>
+      <c r="C75" s="77">
+        <f t="shared" si="8"/>
+        <v>11.32011364</v>
+      </c>
+      <c r="D75" s="78">
         <f>D74/(22*3)</f>
-        <v>3.203515152</v>
+        <v>3.01869697</v>
       </c>
       <c r="E75" s="3"/>
       <c r="F75" s="1"/>
@@ -4365,15 +4346,15 @@
     </row>
     <row r="78" ht="27.75" customHeight="1">
       <c r="A78" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="B78" s="70" t="s">
-        <v>120</v>
-      </c>
-      <c r="C78" s="71"/>
-      <c r="D78" s="58"/>
-      <c r="E78" s="57"/>
-      <c r="F78" s="72"/>
+        <v>115</v>
+      </c>
+      <c r="B78" s="79" t="s">
+        <v>116</v>
+      </c>
+      <c r="C78" s="80"/>
+      <c r="D78" s="67"/>
+      <c r="E78" s="66"/>
+      <c r="F78" s="81"/>
       <c r="G78" s="1"/>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
@@ -4397,20 +4378,20 @@
     </row>
     <row r="79" ht="27.75" customHeight="1">
       <c r="A79" s="1"/>
-      <c r="B79" s="44" t="s">
+      <c r="B79" s="53" t="s">
+        <v>117</v>
+      </c>
+      <c r="C79" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="D79" s="70" t="s">
+        <v>119</v>
+      </c>
+      <c r="E79" s="70" t="s">
+        <v>120</v>
+      </c>
+      <c r="F79" s="70" t="s">
         <v>121</v>
-      </c>
-      <c r="C79" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="D79" s="61" t="s">
-        <v>123</v>
-      </c>
-      <c r="E79" s="61" t="s">
-        <v>124</v>
-      </c>
-      <c r="F79" s="61" t="s">
-        <v>125</v>
       </c>
       <c r="G79" s="1"/>
       <c r="H79" s="1"/>
@@ -4435,23 +4416,23 @@
     </row>
     <row r="80" ht="27.75" customHeight="1">
       <c r="A80" s="1"/>
-      <c r="B80" s="73" t="s">
-        <v>126</v>
-      </c>
-      <c r="C80" s="74">
+      <c r="B80" s="82" t="s">
+        <v>122</v>
+      </c>
+      <c r="C80" s="83">
         <v>0.4</v>
       </c>
-      <c r="D80" s="68">
-        <f t="shared" ref="D80:F80" si="11">$C80/$C$80*B$75</f>
-        <v>12.01318182</v>
-      </c>
-      <c r="E80" s="68">
-        <f t="shared" si="11"/>
-        <v>12.01318182</v>
-      </c>
-      <c r="F80" s="68">
-        <f t="shared" si="11"/>
-        <v>3.203515152</v>
+      <c r="D80" s="77">
+        <f t="shared" ref="D80:F80" si="9">$C80/$C$80*B$75</f>
+        <v>11.32011364</v>
+      </c>
+      <c r="E80" s="77">
+        <f t="shared" si="9"/>
+        <v>11.32011364</v>
+      </c>
+      <c r="F80" s="77">
+        <f t="shared" si="9"/>
+        <v>3.01869697</v>
       </c>
       <c r="G80" s="1"/>
       <c r="H80" s="1"/>
@@ -4476,24 +4457,24 @@
     </row>
     <row r="81" ht="27.75" customHeight="1">
       <c r="A81" s="1"/>
-      <c r="B81" s="73" t="s">
-        <v>127</v>
-      </c>
-      <c r="C81" s="74">
+      <c r="B81" s="82" t="s">
+        <v>123</v>
+      </c>
+      <c r="C81" s="83">
         <f>1-C80</f>
         <v>0.6</v>
       </c>
-      <c r="D81" s="63">
-        <f t="shared" ref="D81:F81" si="12">$C81/$C$80*B$75</f>
-        <v>18.01977273</v>
-      </c>
-      <c r="E81" s="63">
-        <f t="shared" si="12"/>
-        <v>18.01977273</v>
-      </c>
-      <c r="F81" s="63">
-        <f t="shared" si="12"/>
-        <v>4.805272727</v>
+      <c r="D81" s="72">
+        <f t="shared" ref="D81:F81" si="10">$C81/$C$80*B$75</f>
+        <v>16.98017045</v>
+      </c>
+      <c r="E81" s="72">
+        <f t="shared" si="10"/>
+        <v>16.98017045</v>
+      </c>
+      <c r="F81" s="72">
+        <f t="shared" si="10"/>
+        <v>4.528045455</v>
       </c>
       <c r="G81" s="1"/>
       <c r="H81" s="1"/>
@@ -4518,22 +4499,22 @@
     </row>
     <row r="82" ht="27.75" customHeight="1">
       <c r="A82" s="1"/>
-      <c r="B82" s="75"/>
-      <c r="C82" s="74">
+      <c r="B82" s="84"/>
+      <c r="C82" s="83">
         <f>SUM(C80:C81)</f>
         <v>1</v>
       </c>
-      <c r="D82" s="68">
-        <f t="shared" ref="D82:F82" si="13">$C82/$C$80*B$75</f>
-        <v>30.03295455</v>
-      </c>
-      <c r="E82" s="68">
-        <f t="shared" si="13"/>
-        <v>30.03295455</v>
-      </c>
-      <c r="F82" s="68">
-        <f t="shared" si="13"/>
-        <v>8.008787879</v>
+      <c r="D82" s="77">
+        <f t="shared" ref="D82:F82" si="11">$C82/$C$80*B$75</f>
+        <v>28.30028409</v>
+      </c>
+      <c r="E82" s="77">
+        <f t="shared" si="11"/>
+        <v>28.30028409</v>
+      </c>
+      <c r="F82" s="77">
+        <f t="shared" si="11"/>
+        <v>7.546742424</v>
       </c>
       <c r="G82" s="1"/>
       <c r="H82" s="1"/>
@@ -4586,7 +4567,7 @@
     </row>
     <row r="84" ht="27.75" customHeight="1">
       <c r="A84" s="18" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B84" s="25">
         <v>5.0</v>
@@ -4646,16 +4627,16 @@
     </row>
     <row r="86" ht="27.75" customHeight="1">
       <c r="A86" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="B86" s="61" t="s">
-        <v>130</v>
-      </c>
-      <c r="C86" s="61" t="s">
-        <v>131</v>
-      </c>
-      <c r="D86" s="61" t="s">
-        <v>132</v>
+        <v>125</v>
+      </c>
+      <c r="B86" s="70" t="s">
+        <v>126</v>
+      </c>
+      <c r="C86" s="70" t="s">
+        <v>127</v>
+      </c>
+      <c r="D86" s="70" t="s">
+        <v>128</v>
       </c>
       <c r="E86" s="3"/>
       <c r="F86" s="1"/>
@@ -4681,22 +4662,22 @@
       <c r="Z86" s="1"/>
     </row>
     <row r="87" ht="27.75" customHeight="1">
-      <c r="A87" s="76"/>
-      <c r="B87" s="77">
+      <c r="A87" s="85"/>
+      <c r="B87" s="86">
         <f>$D$82/$B$84</f>
-        <v>6.006590909</v>
-      </c>
-      <c r="C87" s="77">
+        <v>5.660056818</v>
+      </c>
+      <c r="C87" s="86">
         <f>$E$82/$B$84</f>
-        <v>6.006590909</v>
-      </c>
-      <c r="D87" s="77">
+        <v>5.660056818</v>
+      </c>
+      <c r="D87" s="86">
         <f>$F$82/$B$84</f>
-        <v>1.601757576</v>
-      </c>
-      <c r="E87" s="76"/>
-      <c r="F87" s="76"/>
-      <c r="G87" s="76"/>
+        <v>1.509348485</v>
+      </c>
+      <c r="E87" s="85"/>
+      <c r="F87" s="85"/>
+      <c r="G87" s="85"/>
       <c r="H87" s="1"/>
       <c r="I87" s="1"/>
       <c r="J87" s="1"/>
@@ -4718,452 +4699,452 @@
       <c r="Z87" s="1"/>
     </row>
     <row r="88" ht="27.75" customHeight="1">
-      <c r="A88" s="76"/>
-      <c r="B88" s="76"/>
-      <c r="C88" s="76"/>
-      <c r="D88" s="76"/>
-      <c r="E88" s="78"/>
-      <c r="F88" s="76"/>
-      <c r="G88" s="76"/>
-      <c r="H88" s="76"/>
-      <c r="I88" s="76"/>
-      <c r="J88" s="76"/>
-      <c r="K88" s="76"/>
-      <c r="L88" s="76"/>
-      <c r="M88" s="76"/>
-      <c r="N88" s="76"/>
-      <c r="O88" s="76"/>
-      <c r="P88" s="76"/>
-      <c r="Q88" s="76"/>
-      <c r="R88" s="76"/>
-      <c r="S88" s="76"/>
-      <c r="T88" s="76"/>
-      <c r="U88" s="76"/>
-      <c r="V88" s="76"/>
-      <c r="W88" s="76"/>
-      <c r="X88" s="76"/>
-      <c r="Y88" s="76"/>
-      <c r="Z88" s="76"/>
+      <c r="A88" s="85"/>
+      <c r="B88" s="85"/>
+      <c r="C88" s="85"/>
+      <c r="D88" s="85"/>
+      <c r="E88" s="87"/>
+      <c r="F88" s="85"/>
+      <c r="G88" s="85"/>
+      <c r="H88" s="85"/>
+      <c r="I88" s="85"/>
+      <c r="J88" s="85"/>
+      <c r="K88" s="85"/>
+      <c r="L88" s="85"/>
+      <c r="M88" s="85"/>
+      <c r="N88" s="85"/>
+      <c r="O88" s="85"/>
+      <c r="P88" s="85"/>
+      <c r="Q88" s="85"/>
+      <c r="R88" s="85"/>
+      <c r="S88" s="85"/>
+      <c r="T88" s="85"/>
+      <c r="U88" s="85"/>
+      <c r="V88" s="85"/>
+      <c r="W88" s="85"/>
+      <c r="X88" s="85"/>
+      <c r="Y88" s="85"/>
+      <c r="Z88" s="85"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="76"/>
-      <c r="B89" s="76"/>
-      <c r="C89" s="76"/>
-      <c r="D89" s="76"/>
-      <c r="E89" s="78"/>
-      <c r="F89" s="76"/>
-      <c r="G89" s="76"/>
-      <c r="H89" s="76"/>
-      <c r="I89" s="76"/>
-      <c r="J89" s="76"/>
-      <c r="K89" s="76"/>
-      <c r="L89" s="76"/>
-      <c r="M89" s="76"/>
-      <c r="N89" s="76"/>
-      <c r="O89" s="76"/>
-      <c r="P89" s="76"/>
-      <c r="Q89" s="76"/>
-      <c r="R89" s="76"/>
-      <c r="S89" s="76"/>
-      <c r="T89" s="76"/>
-      <c r="U89" s="76"/>
-      <c r="V89" s="76"/>
-      <c r="W89" s="76"/>
-      <c r="X89" s="76"/>
-      <c r="Y89" s="76"/>
-      <c r="Z89" s="76"/>
+      <c r="A89" s="85"/>
+      <c r="B89" s="85"/>
+      <c r="C89" s="85"/>
+      <c r="D89" s="85"/>
+      <c r="E89" s="87"/>
+      <c r="F89" s="85"/>
+      <c r="G89" s="85"/>
+      <c r="H89" s="85"/>
+      <c r="I89" s="85"/>
+      <c r="J89" s="85"/>
+      <c r="K89" s="85"/>
+      <c r="L89" s="85"/>
+      <c r="M89" s="85"/>
+      <c r="N89" s="85"/>
+      <c r="O89" s="85"/>
+      <c r="P89" s="85"/>
+      <c r="Q89" s="85"/>
+      <c r="R89" s="85"/>
+      <c r="S89" s="85"/>
+      <c r="T89" s="85"/>
+      <c r="U89" s="85"/>
+      <c r="V89" s="85"/>
+      <c r="W89" s="85"/>
+      <c r="X89" s="85"/>
+      <c r="Y89" s="85"/>
+      <c r="Z89" s="85"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="76"/>
-      <c r="B90" s="76"/>
-      <c r="C90" s="76"/>
-      <c r="D90" s="76"/>
-      <c r="E90" s="78"/>
-      <c r="F90" s="76"/>
-      <c r="G90" s="76"/>
-      <c r="H90" s="76"/>
-      <c r="I90" s="76"/>
-      <c r="J90" s="76"/>
-      <c r="K90" s="76"/>
-      <c r="L90" s="76"/>
-      <c r="M90" s="76"/>
-      <c r="N90" s="76"/>
-      <c r="O90" s="76"/>
-      <c r="P90" s="76"/>
-      <c r="Q90" s="76"/>
-      <c r="R90" s="76"/>
-      <c r="S90" s="76"/>
-      <c r="T90" s="76"/>
-      <c r="U90" s="76"/>
-      <c r="V90" s="76"/>
-      <c r="W90" s="76"/>
-      <c r="X90" s="76"/>
-      <c r="Y90" s="76"/>
-      <c r="Z90" s="76"/>
+      <c r="A90" s="85"/>
+      <c r="B90" s="85"/>
+      <c r="C90" s="85"/>
+      <c r="D90" s="85"/>
+      <c r="E90" s="87"/>
+      <c r="F90" s="85"/>
+      <c r="G90" s="85"/>
+      <c r="H90" s="85"/>
+      <c r="I90" s="85"/>
+      <c r="J90" s="85"/>
+      <c r="K90" s="85"/>
+      <c r="L90" s="85"/>
+      <c r="M90" s="85"/>
+      <c r="N90" s="85"/>
+      <c r="O90" s="85"/>
+      <c r="P90" s="85"/>
+      <c r="Q90" s="85"/>
+      <c r="R90" s="85"/>
+      <c r="S90" s="85"/>
+      <c r="T90" s="85"/>
+      <c r="U90" s="85"/>
+      <c r="V90" s="85"/>
+      <c r="W90" s="85"/>
+      <c r="X90" s="85"/>
+      <c r="Y90" s="85"/>
+      <c r="Z90" s="85"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="76"/>
-      <c r="B91" s="76"/>
-      <c r="C91" s="76"/>
-      <c r="D91" s="76"/>
-      <c r="E91" s="78"/>
-      <c r="F91" s="76"/>
-      <c r="G91" s="76"/>
-      <c r="H91" s="76"/>
-      <c r="I91" s="76"/>
-      <c r="J91" s="76"/>
-      <c r="K91" s="76"/>
-      <c r="L91" s="76"/>
-      <c r="M91" s="76"/>
-      <c r="N91" s="76"/>
-      <c r="O91" s="76"/>
-      <c r="P91" s="76"/>
-      <c r="Q91" s="76"/>
-      <c r="R91" s="76"/>
-      <c r="S91" s="76"/>
-      <c r="T91" s="76"/>
-      <c r="U91" s="76"/>
-      <c r="V91" s="76"/>
-      <c r="W91" s="76"/>
-      <c r="X91" s="76"/>
-      <c r="Y91" s="76"/>
-      <c r="Z91" s="76"/>
+      <c r="A91" s="85"/>
+      <c r="B91" s="85"/>
+      <c r="C91" s="85"/>
+      <c r="D91" s="85"/>
+      <c r="E91" s="87"/>
+      <c r="F91" s="85"/>
+      <c r="G91" s="85"/>
+      <c r="H91" s="85"/>
+      <c r="I91" s="85"/>
+      <c r="J91" s="85"/>
+      <c r="K91" s="85"/>
+      <c r="L91" s="85"/>
+      <c r="M91" s="85"/>
+      <c r="N91" s="85"/>
+      <c r="O91" s="85"/>
+      <c r="P91" s="85"/>
+      <c r="Q91" s="85"/>
+      <c r="R91" s="85"/>
+      <c r="S91" s="85"/>
+      <c r="T91" s="85"/>
+      <c r="U91" s="85"/>
+      <c r="V91" s="85"/>
+      <c r="W91" s="85"/>
+      <c r="X91" s="85"/>
+      <c r="Y91" s="85"/>
+      <c r="Z91" s="85"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="76"/>
-      <c r="B92" s="76"/>
-      <c r="C92" s="76"/>
-      <c r="D92" s="76"/>
-      <c r="E92" s="78"/>
-      <c r="F92" s="76"/>
-      <c r="G92" s="76"/>
-      <c r="H92" s="76"/>
-      <c r="I92" s="76"/>
-      <c r="J92" s="76"/>
-      <c r="K92" s="76"/>
-      <c r="L92" s="76"/>
-      <c r="M92" s="76"/>
-      <c r="N92" s="76"/>
-      <c r="O92" s="76"/>
-      <c r="P92" s="76"/>
-      <c r="Q92" s="76"/>
-      <c r="R92" s="76"/>
-      <c r="S92" s="76"/>
-      <c r="T92" s="76"/>
-      <c r="U92" s="76"/>
-      <c r="V92" s="76"/>
-      <c r="W92" s="76"/>
-      <c r="X92" s="76"/>
-      <c r="Y92" s="76"/>
-      <c r="Z92" s="76"/>
+      <c r="A92" s="85"/>
+      <c r="B92" s="85"/>
+      <c r="C92" s="85"/>
+      <c r="D92" s="85"/>
+      <c r="E92" s="87"/>
+      <c r="F92" s="85"/>
+      <c r="G92" s="85"/>
+      <c r="H92" s="85"/>
+      <c r="I92" s="85"/>
+      <c r="J92" s="85"/>
+      <c r="K92" s="85"/>
+      <c r="L92" s="85"/>
+      <c r="M92" s="85"/>
+      <c r="N92" s="85"/>
+      <c r="O92" s="85"/>
+      <c r="P92" s="85"/>
+      <c r="Q92" s="85"/>
+      <c r="R92" s="85"/>
+      <c r="S92" s="85"/>
+      <c r="T92" s="85"/>
+      <c r="U92" s="85"/>
+      <c r="V92" s="85"/>
+      <c r="W92" s="85"/>
+      <c r="X92" s="85"/>
+      <c r="Y92" s="85"/>
+      <c r="Z92" s="85"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="76"/>
-      <c r="B93" s="76"/>
-      <c r="C93" s="76"/>
-      <c r="D93" s="76"/>
-      <c r="E93" s="78"/>
-      <c r="F93" s="76"/>
-      <c r="G93" s="76"/>
-      <c r="H93" s="76"/>
-      <c r="I93" s="76"/>
-      <c r="J93" s="76"/>
-      <c r="K93" s="76"/>
-      <c r="L93" s="76"/>
-      <c r="M93" s="76"/>
-      <c r="N93" s="76"/>
-      <c r="O93" s="76"/>
-      <c r="P93" s="76"/>
-      <c r="Q93" s="76"/>
-      <c r="R93" s="76"/>
-      <c r="S93" s="76"/>
-      <c r="T93" s="76"/>
-      <c r="U93" s="76"/>
-      <c r="V93" s="76"/>
-      <c r="W93" s="76"/>
-      <c r="X93" s="76"/>
-      <c r="Y93" s="76"/>
-      <c r="Z93" s="76"/>
+      <c r="A93" s="85"/>
+      <c r="B93" s="85"/>
+      <c r="C93" s="85"/>
+      <c r="D93" s="85"/>
+      <c r="E93" s="87"/>
+      <c r="F93" s="85"/>
+      <c r="G93" s="85"/>
+      <c r="H93" s="85"/>
+      <c r="I93" s="85"/>
+      <c r="J93" s="85"/>
+      <c r="K93" s="85"/>
+      <c r="L93" s="85"/>
+      <c r="M93" s="85"/>
+      <c r="N93" s="85"/>
+      <c r="O93" s="85"/>
+      <c r="P93" s="85"/>
+      <c r="Q93" s="85"/>
+      <c r="R93" s="85"/>
+      <c r="S93" s="85"/>
+      <c r="T93" s="85"/>
+      <c r="U93" s="85"/>
+      <c r="V93" s="85"/>
+      <c r="W93" s="85"/>
+      <c r="X93" s="85"/>
+      <c r="Y93" s="85"/>
+      <c r="Z93" s="85"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="76"/>
-      <c r="B94" s="76"/>
-      <c r="C94" s="76"/>
-      <c r="D94" s="76"/>
-      <c r="E94" s="78"/>
-      <c r="F94" s="76"/>
-      <c r="G94" s="76"/>
-      <c r="H94" s="76"/>
-      <c r="I94" s="76"/>
-      <c r="J94" s="76"/>
-      <c r="K94" s="76"/>
-      <c r="L94" s="76"/>
-      <c r="M94" s="76"/>
-      <c r="N94" s="76"/>
-      <c r="O94" s="76"/>
-      <c r="P94" s="76"/>
-      <c r="Q94" s="76"/>
-      <c r="R94" s="76"/>
-      <c r="S94" s="76"/>
-      <c r="T94" s="76"/>
-      <c r="U94" s="76"/>
-      <c r="V94" s="76"/>
-      <c r="W94" s="76"/>
-      <c r="X94" s="76"/>
-      <c r="Y94" s="76"/>
-      <c r="Z94" s="76"/>
+      <c r="A94" s="85"/>
+      <c r="B94" s="85"/>
+      <c r="C94" s="85"/>
+      <c r="D94" s="85"/>
+      <c r="E94" s="87"/>
+      <c r="F94" s="85"/>
+      <c r="G94" s="85"/>
+      <c r="H94" s="85"/>
+      <c r="I94" s="85"/>
+      <c r="J94" s="85"/>
+      <c r="K94" s="85"/>
+      <c r="L94" s="85"/>
+      <c r="M94" s="85"/>
+      <c r="N94" s="85"/>
+      <c r="O94" s="85"/>
+      <c r="P94" s="85"/>
+      <c r="Q94" s="85"/>
+      <c r="R94" s="85"/>
+      <c r="S94" s="85"/>
+      <c r="T94" s="85"/>
+      <c r="U94" s="85"/>
+      <c r="V94" s="85"/>
+      <c r="W94" s="85"/>
+      <c r="X94" s="85"/>
+      <c r="Y94" s="85"/>
+      <c r="Z94" s="85"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="76"/>
-      <c r="B95" s="76"/>
-      <c r="C95" s="76"/>
-      <c r="D95" s="76"/>
-      <c r="E95" s="78"/>
-      <c r="F95" s="76"/>
-      <c r="G95" s="76"/>
-      <c r="H95" s="76"/>
-      <c r="I95" s="76"/>
-      <c r="J95" s="76"/>
-      <c r="K95" s="76"/>
-      <c r="L95" s="76"/>
-      <c r="M95" s="76"/>
-      <c r="N95" s="76"/>
-      <c r="O95" s="76"/>
-      <c r="P95" s="76"/>
-      <c r="Q95" s="76"/>
-      <c r="R95" s="76"/>
-      <c r="S95" s="76"/>
-      <c r="T95" s="76"/>
-      <c r="U95" s="76"/>
-      <c r="V95" s="76"/>
-      <c r="W95" s="76"/>
-      <c r="X95" s="76"/>
-      <c r="Y95" s="76"/>
-      <c r="Z95" s="76"/>
+      <c r="A95" s="85"/>
+      <c r="B95" s="85"/>
+      <c r="C95" s="85"/>
+      <c r="D95" s="85"/>
+      <c r="E95" s="87"/>
+      <c r="F95" s="85"/>
+      <c r="G95" s="85"/>
+      <c r="H95" s="85"/>
+      <c r="I95" s="85"/>
+      <c r="J95" s="85"/>
+      <c r="K95" s="85"/>
+      <c r="L95" s="85"/>
+      <c r="M95" s="85"/>
+      <c r="N95" s="85"/>
+      <c r="O95" s="85"/>
+      <c r="P95" s="85"/>
+      <c r="Q95" s="85"/>
+      <c r="R95" s="85"/>
+      <c r="S95" s="85"/>
+      <c r="T95" s="85"/>
+      <c r="U95" s="85"/>
+      <c r="V95" s="85"/>
+      <c r="W95" s="85"/>
+      <c r="X95" s="85"/>
+      <c r="Y95" s="85"/>
+      <c r="Z95" s="85"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="76"/>
-      <c r="B96" s="76"/>
-      <c r="C96" s="76"/>
-      <c r="D96" s="76"/>
-      <c r="E96" s="78"/>
-      <c r="F96" s="76"/>
-      <c r="G96" s="76"/>
-      <c r="H96" s="76"/>
-      <c r="I96" s="76"/>
-      <c r="J96" s="76"/>
-      <c r="K96" s="76"/>
-      <c r="L96" s="76"/>
-      <c r="M96" s="76"/>
-      <c r="N96" s="76"/>
-      <c r="O96" s="76"/>
-      <c r="P96" s="76"/>
-      <c r="Q96" s="76"/>
-      <c r="R96" s="76"/>
-      <c r="S96" s="76"/>
-      <c r="T96" s="76"/>
-      <c r="U96" s="76"/>
-      <c r="V96" s="76"/>
-      <c r="W96" s="76"/>
-      <c r="X96" s="76"/>
-      <c r="Y96" s="76"/>
-      <c r="Z96" s="76"/>
+      <c r="A96" s="85"/>
+      <c r="B96" s="85"/>
+      <c r="C96" s="85"/>
+      <c r="D96" s="85"/>
+      <c r="E96" s="87"/>
+      <c r="F96" s="85"/>
+      <c r="G96" s="85"/>
+      <c r="H96" s="85"/>
+      <c r="I96" s="85"/>
+      <c r="J96" s="85"/>
+      <c r="K96" s="85"/>
+      <c r="L96" s="85"/>
+      <c r="M96" s="85"/>
+      <c r="N96" s="85"/>
+      <c r="O96" s="85"/>
+      <c r="P96" s="85"/>
+      <c r="Q96" s="85"/>
+      <c r="R96" s="85"/>
+      <c r="S96" s="85"/>
+      <c r="T96" s="85"/>
+      <c r="U96" s="85"/>
+      <c r="V96" s="85"/>
+      <c r="W96" s="85"/>
+      <c r="X96" s="85"/>
+      <c r="Y96" s="85"/>
+      <c r="Z96" s="85"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="76"/>
-      <c r="B97" s="76"/>
-      <c r="C97" s="76"/>
-      <c r="D97" s="76"/>
-      <c r="E97" s="78"/>
-      <c r="F97" s="76"/>
-      <c r="G97" s="76"/>
-      <c r="H97" s="76"/>
-      <c r="I97" s="76"/>
-      <c r="J97" s="76"/>
-      <c r="K97" s="76"/>
-      <c r="L97" s="76"/>
-      <c r="M97" s="76"/>
-      <c r="N97" s="76"/>
-      <c r="O97" s="76"/>
-      <c r="P97" s="76"/>
-      <c r="Q97" s="76"/>
-      <c r="R97" s="76"/>
-      <c r="S97" s="76"/>
-      <c r="T97" s="76"/>
-      <c r="U97" s="76"/>
-      <c r="V97" s="76"/>
-      <c r="W97" s="76"/>
-      <c r="X97" s="76"/>
-      <c r="Y97" s="76"/>
-      <c r="Z97" s="76"/>
+      <c r="A97" s="85"/>
+      <c r="B97" s="85"/>
+      <c r="C97" s="85"/>
+      <c r="D97" s="85"/>
+      <c r="E97" s="87"/>
+      <c r="F97" s="85"/>
+      <c r="G97" s="85"/>
+      <c r="H97" s="85"/>
+      <c r="I97" s="85"/>
+      <c r="J97" s="85"/>
+      <c r="K97" s="85"/>
+      <c r="L97" s="85"/>
+      <c r="M97" s="85"/>
+      <c r="N97" s="85"/>
+      <c r="O97" s="85"/>
+      <c r="P97" s="85"/>
+      <c r="Q97" s="85"/>
+      <c r="R97" s="85"/>
+      <c r="S97" s="85"/>
+      <c r="T97" s="85"/>
+      <c r="U97" s="85"/>
+      <c r="V97" s="85"/>
+      <c r="W97" s="85"/>
+      <c r="X97" s="85"/>
+      <c r="Y97" s="85"/>
+      <c r="Z97" s="85"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="76"/>
-      <c r="B98" s="76"/>
-      <c r="C98" s="76"/>
-      <c r="D98" s="76"/>
-      <c r="E98" s="78"/>
-      <c r="F98" s="76"/>
-      <c r="G98" s="76"/>
-      <c r="H98" s="76"/>
-      <c r="I98" s="76"/>
-      <c r="J98" s="76"/>
-      <c r="K98" s="76"/>
-      <c r="L98" s="76"/>
-      <c r="M98" s="76"/>
-      <c r="N98" s="76"/>
-      <c r="O98" s="76"/>
-      <c r="P98" s="76"/>
-      <c r="Q98" s="76"/>
-      <c r="R98" s="76"/>
-      <c r="S98" s="76"/>
-      <c r="T98" s="76"/>
-      <c r="U98" s="76"/>
-      <c r="V98" s="76"/>
-      <c r="W98" s="76"/>
-      <c r="X98" s="76"/>
-      <c r="Y98" s="76"/>
-      <c r="Z98" s="76"/>
+      <c r="A98" s="85"/>
+      <c r="B98" s="85"/>
+      <c r="C98" s="85"/>
+      <c r="D98" s="85"/>
+      <c r="E98" s="87"/>
+      <c r="F98" s="85"/>
+      <c r="G98" s="85"/>
+      <c r="H98" s="85"/>
+      <c r="I98" s="85"/>
+      <c r="J98" s="85"/>
+      <c r="K98" s="85"/>
+      <c r="L98" s="85"/>
+      <c r="M98" s="85"/>
+      <c r="N98" s="85"/>
+      <c r="O98" s="85"/>
+      <c r="P98" s="85"/>
+      <c r="Q98" s="85"/>
+      <c r="R98" s="85"/>
+      <c r="S98" s="85"/>
+      <c r="T98" s="85"/>
+      <c r="U98" s="85"/>
+      <c r="V98" s="85"/>
+      <c r="W98" s="85"/>
+      <c r="X98" s="85"/>
+      <c r="Y98" s="85"/>
+      <c r="Z98" s="85"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="76"/>
-      <c r="B99" s="76"/>
-      <c r="C99" s="76"/>
-      <c r="D99" s="76"/>
-      <c r="E99" s="78"/>
-      <c r="F99" s="76"/>
-      <c r="G99" s="76"/>
-      <c r="H99" s="76"/>
-      <c r="I99" s="76"/>
-      <c r="J99" s="76"/>
-      <c r="K99" s="76"/>
-      <c r="L99" s="76"/>
-      <c r="M99" s="76"/>
-      <c r="N99" s="76"/>
-      <c r="O99" s="76"/>
-      <c r="P99" s="76"/>
-      <c r="Q99" s="76"/>
-      <c r="R99" s="76"/>
-      <c r="S99" s="76"/>
-      <c r="T99" s="76"/>
-      <c r="U99" s="76"/>
-      <c r="V99" s="76"/>
-      <c r="W99" s="76"/>
-      <c r="X99" s="76"/>
-      <c r="Y99" s="76"/>
-      <c r="Z99" s="76"/>
+      <c r="A99" s="85"/>
+      <c r="B99" s="85"/>
+      <c r="C99" s="85"/>
+      <c r="D99" s="85"/>
+      <c r="E99" s="87"/>
+      <c r="F99" s="85"/>
+      <c r="G99" s="85"/>
+      <c r="H99" s="85"/>
+      <c r="I99" s="85"/>
+      <c r="J99" s="85"/>
+      <c r="K99" s="85"/>
+      <c r="L99" s="85"/>
+      <c r="M99" s="85"/>
+      <c r="N99" s="85"/>
+      <c r="O99" s="85"/>
+      <c r="P99" s="85"/>
+      <c r="Q99" s="85"/>
+      <c r="R99" s="85"/>
+      <c r="S99" s="85"/>
+      <c r="T99" s="85"/>
+      <c r="U99" s="85"/>
+      <c r="V99" s="85"/>
+      <c r="W99" s="85"/>
+      <c r="X99" s="85"/>
+      <c r="Y99" s="85"/>
+      <c r="Z99" s="85"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="76"/>
-      <c r="B100" s="76"/>
-      <c r="C100" s="76"/>
-      <c r="D100" s="76"/>
-      <c r="E100" s="78"/>
-      <c r="F100" s="76"/>
-      <c r="G100" s="76"/>
-      <c r="H100" s="76"/>
-      <c r="I100" s="76"/>
-      <c r="J100" s="76"/>
-      <c r="K100" s="76"/>
-      <c r="L100" s="76"/>
-      <c r="M100" s="76"/>
-      <c r="N100" s="76"/>
-      <c r="O100" s="76"/>
-      <c r="P100" s="76"/>
-      <c r="Q100" s="76"/>
-      <c r="R100" s="76"/>
-      <c r="S100" s="76"/>
-      <c r="T100" s="76"/>
-      <c r="U100" s="76"/>
-      <c r="V100" s="76"/>
-      <c r="W100" s="76"/>
-      <c r="X100" s="76"/>
-      <c r="Y100" s="76"/>
-      <c r="Z100" s="76"/>
+      <c r="A100" s="85"/>
+      <c r="B100" s="85"/>
+      <c r="C100" s="85"/>
+      <c r="D100" s="85"/>
+      <c r="E100" s="87"/>
+      <c r="F100" s="85"/>
+      <c r="G100" s="85"/>
+      <c r="H100" s="85"/>
+      <c r="I100" s="85"/>
+      <c r="J100" s="85"/>
+      <c r="K100" s="85"/>
+      <c r="L100" s="85"/>
+      <c r="M100" s="85"/>
+      <c r="N100" s="85"/>
+      <c r="O100" s="85"/>
+      <c r="P100" s="85"/>
+      <c r="Q100" s="85"/>
+      <c r="R100" s="85"/>
+      <c r="S100" s="85"/>
+      <c r="T100" s="85"/>
+      <c r="U100" s="85"/>
+      <c r="V100" s="85"/>
+      <c r="W100" s="85"/>
+      <c r="X100" s="85"/>
+      <c r="Y100" s="85"/>
+      <c r="Z100" s="85"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="76"/>
-      <c r="B101" s="76"/>
-      <c r="C101" s="76"/>
-      <c r="D101" s="76"/>
-      <c r="E101" s="78"/>
-      <c r="F101" s="76"/>
-      <c r="G101" s="76"/>
-      <c r="H101" s="76"/>
-      <c r="I101" s="76"/>
-      <c r="J101" s="76"/>
-      <c r="K101" s="76"/>
-      <c r="L101" s="76"/>
-      <c r="M101" s="76"/>
-      <c r="N101" s="76"/>
-      <c r="O101" s="76"/>
-      <c r="P101" s="76"/>
-      <c r="Q101" s="76"/>
-      <c r="R101" s="76"/>
-      <c r="S101" s="76"/>
-      <c r="T101" s="76"/>
-      <c r="U101" s="76"/>
-      <c r="V101" s="76"/>
-      <c r="W101" s="76"/>
-      <c r="X101" s="76"/>
-      <c r="Y101" s="76"/>
-      <c r="Z101" s="76"/>
+      <c r="A101" s="85"/>
+      <c r="B101" s="85"/>
+      <c r="C101" s="85"/>
+      <c r="D101" s="85"/>
+      <c r="E101" s="87"/>
+      <c r="F101" s="85"/>
+      <c r="G101" s="85"/>
+      <c r="H101" s="85"/>
+      <c r="I101" s="85"/>
+      <c r="J101" s="85"/>
+      <c r="K101" s="85"/>
+      <c r="L101" s="85"/>
+      <c r="M101" s="85"/>
+      <c r="N101" s="85"/>
+      <c r="O101" s="85"/>
+      <c r="P101" s="85"/>
+      <c r="Q101" s="85"/>
+      <c r="R101" s="85"/>
+      <c r="S101" s="85"/>
+      <c r="T101" s="85"/>
+      <c r="U101" s="85"/>
+      <c r="V101" s="85"/>
+      <c r="W101" s="85"/>
+      <c r="X101" s="85"/>
+      <c r="Y101" s="85"/>
+      <c r="Z101" s="85"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="76"/>
-      <c r="B102" s="76"/>
-      <c r="C102" s="76"/>
-      <c r="D102" s="76"/>
-      <c r="E102" s="78"/>
-      <c r="F102" s="76"/>
-      <c r="G102" s="76"/>
-      <c r="H102" s="76"/>
-      <c r="I102" s="76"/>
-      <c r="J102" s="76"/>
-      <c r="K102" s="76"/>
-      <c r="L102" s="76"/>
-      <c r="M102" s="76"/>
-      <c r="N102" s="76"/>
-      <c r="O102" s="76"/>
-      <c r="P102" s="76"/>
-      <c r="Q102" s="76"/>
-      <c r="R102" s="76"/>
-      <c r="S102" s="76"/>
-      <c r="T102" s="76"/>
-      <c r="U102" s="76"/>
-      <c r="V102" s="76"/>
-      <c r="W102" s="76"/>
-      <c r="X102" s="76"/>
-      <c r="Y102" s="76"/>
-      <c r="Z102" s="76"/>
+      <c r="A102" s="85"/>
+      <c r="B102" s="85"/>
+      <c r="C102" s="85"/>
+      <c r="D102" s="85"/>
+      <c r="E102" s="87"/>
+      <c r="F102" s="85"/>
+      <c r="G102" s="85"/>
+      <c r="H102" s="85"/>
+      <c r="I102" s="85"/>
+      <c r="J102" s="85"/>
+      <c r="K102" s="85"/>
+      <c r="L102" s="85"/>
+      <c r="M102" s="85"/>
+      <c r="N102" s="85"/>
+      <c r="O102" s="85"/>
+      <c r="P102" s="85"/>
+      <c r="Q102" s="85"/>
+      <c r="R102" s="85"/>
+      <c r="S102" s="85"/>
+      <c r="T102" s="85"/>
+      <c r="U102" s="85"/>
+      <c r="V102" s="85"/>
+      <c r="W102" s="85"/>
+      <c r="X102" s="85"/>
+      <c r="Y102" s="85"/>
+      <c r="Z102" s="85"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="76"/>
-      <c r="B103" s="76"/>
-      <c r="C103" s="76"/>
-      <c r="D103" s="76"/>
-      <c r="E103" s="78"/>
-      <c r="F103" s="76"/>
-      <c r="G103" s="76"/>
-      <c r="H103" s="76"/>
-      <c r="I103" s="76"/>
-      <c r="J103" s="76"/>
-      <c r="K103" s="76"/>
-      <c r="L103" s="76"/>
-      <c r="M103" s="76"/>
-      <c r="N103" s="76"/>
-      <c r="O103" s="76"/>
-      <c r="P103" s="76"/>
-      <c r="Q103" s="76"/>
-      <c r="R103" s="76"/>
-      <c r="S103" s="76"/>
-      <c r="T103" s="76"/>
-      <c r="U103" s="76"/>
-      <c r="V103" s="76"/>
-      <c r="W103" s="76"/>
-      <c r="X103" s="76"/>
-      <c r="Y103" s="76"/>
-      <c r="Z103" s="76"/>
+      <c r="A103" s="85"/>
+      <c r="B103" s="85"/>
+      <c r="C103" s="85"/>
+      <c r="D103" s="85"/>
+      <c r="E103" s="87"/>
+      <c r="F103" s="85"/>
+      <c r="G103" s="85"/>
+      <c r="H103" s="85"/>
+      <c r="I103" s="85"/>
+      <c r="J103" s="85"/>
+      <c r="K103" s="85"/>
+      <c r="L103" s="85"/>
+      <c r="M103" s="85"/>
+      <c r="N103" s="85"/>
+      <c r="O103" s="85"/>
+      <c r="P103" s="85"/>
+      <c r="Q103" s="85"/>
+      <c r="R103" s="85"/>
+      <c r="S103" s="85"/>
+      <c r="T103" s="85"/>
+      <c r="U103" s="85"/>
+      <c r="V103" s="85"/>
+      <c r="W103" s="85"/>
+      <c r="X103" s="85"/>
+      <c r="Y103" s="85"/>
+      <c r="Z103" s="85"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="1"/>
@@ -5173,25 +5154,25 @@
       <c r="E104" s="3"/>
       <c r="F104" s="1"/>
       <c r="G104" s="1"/>
-      <c r="H104" s="76"/>
-      <c r="I104" s="76"/>
-      <c r="J104" s="76"/>
-      <c r="K104" s="76"/>
-      <c r="L104" s="76"/>
-      <c r="M104" s="76"/>
-      <c r="N104" s="76"/>
-      <c r="O104" s="76"/>
-      <c r="P104" s="76"/>
-      <c r="Q104" s="76"/>
-      <c r="R104" s="76"/>
-      <c r="S104" s="76"/>
-      <c r="T104" s="76"/>
-      <c r="U104" s="76"/>
-      <c r="V104" s="76"/>
-      <c r="W104" s="76"/>
-      <c r="X104" s="76"/>
-      <c r="Y104" s="76"/>
-      <c r="Z104" s="76"/>
+      <c r="H104" s="85"/>
+      <c r="I104" s="85"/>
+      <c r="J104" s="85"/>
+      <c r="K104" s="85"/>
+      <c r="L104" s="85"/>
+      <c r="M104" s="85"/>
+      <c r="N104" s="85"/>
+      <c r="O104" s="85"/>
+      <c r="P104" s="85"/>
+      <c r="Q104" s="85"/>
+      <c r="R104" s="85"/>
+      <c r="S104" s="85"/>
+      <c r="T104" s="85"/>
+      <c r="U104" s="85"/>
+      <c r="V104" s="85"/>
+      <c r="W104" s="85"/>
+      <c r="X104" s="85"/>
+      <c r="Y104" s="85"/>
+      <c r="Z104" s="85"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="1"/>
